--- a/artfynd/A 55244-2021 artfynd.xlsx
+++ b/artfynd/A 55244-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55244-2021 artfynd.xlsx
+++ b/artfynd/A 55244-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>99114460</v>
       </c>
       <c r="B2" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374711.3312970872</v>
+        <v>374711</v>
       </c>
       <c r="R2" t="n">
-        <v>6921033.594247475</v>
+        <v>6921034</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>99114506</v>
       </c>
       <c r="B3" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>374725.3708065639</v>
+        <v>374726</v>
       </c>
       <c r="R3" t="n">
-        <v>6921023.785810993</v>
+        <v>6921024</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>99114508</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>374720.3699672795</v>
+        <v>374720</v>
       </c>
       <c r="R4" t="n">
-        <v>6921026.757937341</v>
+        <v>6921027</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99114488</v>
+        <v>99114507</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>374705.9198168818</v>
+        <v>374724</v>
       </c>
       <c r="R5" t="n">
-        <v>6921000.847036527</v>
+        <v>6920963</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1066,7 @@
         <v>99114467</v>
       </c>
       <c r="B6" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>374697.2103317513</v>
+        <v>374697</v>
       </c>
       <c r="R6" t="n">
-        <v>6921053.615620567</v>
+        <v>6921054</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>99114488</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övre Mysklan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>374706</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6921001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-03-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55244-2021 artfynd.xlsx
+++ b/artfynd/A 55244-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114460</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114506</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114507</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114467</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114488</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>